--- a/docs/downloads/04/tbl_homeland_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_homeland_alaotra_tous.xlsx
@@ -443,12 +443,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>5.9</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -512,12 +506,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>11.1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -581,12 +569,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>14.3</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -604,12 +586,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>14.3</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -650,12 +626,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D13">
-        <v>3</v>
-      </c>
-      <c r="E13">
-        <v>30</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -673,12 +643,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>10</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -719,12 +683,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <v>16.7</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -765,12 +723,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D18">
-        <v>4</v>
-      </c>
-      <c r="E18">
-        <v>36.4</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -811,12 +763,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>9.1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -834,12 +780,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>9.1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -949,12 +889,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="D26">
-        <v>3</v>
-      </c>
-      <c r="E26">
-        <v>23.1</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -972,12 +906,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D27">
-        <v>3</v>
-      </c>
-      <c r="E27">
-        <v>14.3</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1018,12 +946,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="D29">
-        <v>4</v>
-      </c>
-      <c r="E29">
-        <v>19</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1041,12 +963,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D30">
-        <v>4</v>
-      </c>
-      <c r="E30">
-        <v>40</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1064,12 +980,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D31">
-        <v>3</v>
-      </c>
-      <c r="E31">
-        <v>30</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1087,12 +997,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="D32">
-        <v>3</v>
-      </c>
-      <c r="E32">
-        <v>30</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1110,12 +1014,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D33">
-        <v>2</v>
-      </c>
-      <c r="E33">
-        <v>20</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1156,12 +1054,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="D35">
-        <v>3</v>
-      </c>
-      <c r="E35">
-        <v>30</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1179,12 +1071,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D36">
-        <v>3</v>
-      </c>
-      <c r="E36">
-        <v>27.3</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1202,12 +1088,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D37">
-        <v>3</v>
-      </c>
-      <c r="E37">
-        <v>27.3</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1248,12 +1128,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D39">
-        <v>4</v>
-      </c>
-      <c r="E39">
-        <v>26.7</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1270,12 +1144,6 @@
         <is>
           <t>2</t>
         </is>
-      </c>
-      <c r="D40">
-        <v>4</v>
-      </c>
-      <c r="E40">
-        <v>26.7</v>
       </c>
     </row>
     <row r="41">

--- a/docs/downloads/04/tbl_homeland_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_homeland_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -407,7 +407,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -430,7 +430,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -447,7 +447,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -510,7 +510,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -556,7 +556,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -590,7 +590,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -710,7 +710,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -767,7 +767,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -784,7 +784,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -807,7 +807,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -876,7 +876,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -933,7 +933,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -950,7 +950,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -967,7 +967,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1018,7 +1018,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1058,7 +1058,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1075,7 +1075,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1092,7 +1092,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1115,7 +1115,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1132,7 +1132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1149,7 +1149,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1172,7 +1172,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1195,7 +1195,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1218,7 +1218,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1264,7 +1264,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1287,7 +1287,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">

--- a/docs/downloads/04/tbl_homeland_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_homeland_alaotra_tous.xlsx
@@ -394,7 +394,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D2">
@@ -417,7 +417,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D3">
@@ -440,8 +440,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
+          <t>Dans la commune</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>35.3</v>
       </c>
     </row>
     <row r="5">
@@ -457,14 +463,8 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>35.3</v>
+          <t>Dans le fokontany</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -480,7 +480,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D6">
@@ -503,8 +503,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
+          <t>Dans la commune</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>33.3</v>
       </c>
     </row>
     <row r="8">
@@ -520,14 +526,8 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>6</v>
-      </c>
-      <c r="E8">
-        <v>33.3</v>
+          <t>Dans le fokontany</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -543,7 +543,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D9">
@@ -566,7 +566,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dans la commune</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans le fokontany</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D12">
@@ -623,7 +623,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dans la commune</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans le fokontany</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D15">
@@ -680,7 +680,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans la commune</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D17">
@@ -720,7 +720,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans la commune</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D19">
@@ -760,7 +760,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dans la commune</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans le fokontany</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D22">
@@ -817,7 +817,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D23">
@@ -840,7 +840,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dans la commune</t>
         </is>
       </c>
       <c r="D24">
@@ -863,7 +863,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans le fokontany</t>
         </is>
       </c>
       <c r="D25">
@@ -886,7 +886,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
     </row>
@@ -903,8 +903,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
+          <t>Dans la commune</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>14</v>
+      </c>
+      <c r="E27">
+        <v>66.7</v>
       </c>
     </row>
     <row r="28">
@@ -920,14 +926,8 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>14</v>
-      </c>
-      <c r="E28">
-        <v>66.7</v>
+          <t>Dans le fokontany</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -943,7 +943,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dans la commune</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans le fokontany</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
     </row>
@@ -1011,8 +1011,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
+          <t>Dans la commune</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>5</v>
+      </c>
+      <c r="E33">
+        <v>50</v>
       </c>
     </row>
     <row r="34">
@@ -1028,14 +1034,8 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>5</v>
-      </c>
-      <c r="E34">
-        <v>50</v>
+          <t>Dans le fokontany</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dans la commune</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans le fokontany</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D38">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dans la commune</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans le fokontany</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D41">
@@ -1182,14 +1182,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dans la commune</t>
         </is>
       </c>
       <c r="D42">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E42">
-        <v>15.6</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="43">
@@ -1205,14 +1205,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans le fokontany</t>
         </is>
       </c>
       <c r="D43">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E43">
-        <v>21.9</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="44">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D44">
@@ -1251,14 +1251,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dans la commune</t>
         </is>
       </c>
       <c r="D45">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E45">
-        <v>13.3</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="46">
@@ -1274,14 +1274,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dans le fokontany</t>
         </is>
       </c>
       <c r="D46">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E46">
-        <v>32.4</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="47">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Hors de la commune</t>
         </is>
       </c>
       <c r="D47">
